--- a/attachments/DSJ_AE_Pricing_and_Revenue_Management.xlsx
+++ b/attachments/DSJ_AE_Pricing_and_Revenue_Management.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\liangfeiqiu\Dropbox\UF\Review\DSJ EIC\DSJ EIC\DSJ board\Finalized\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\liangfeiqiu\Dropbox\UF\Review\DSJ EIC\DSJ EIC\DSJ board\Finalized\DSJ AEs and ERBs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D189393B-824C-467A-BBD2-B4E65A88E4E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4CE7532-30A2-4486-9F26-F7C848106E2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12432" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Form Responses 1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Z_B1502E2D_7D13_4985_8030_5AE29C7B5A5F_.wvu.FilterData" localSheetId="0" hidden="1">'Form Responses 1'!$A$1:$L$42</definedName>
+    <definedName name="Z_B1502E2D_7D13_4985_8030_5AE29C7B5A5F_.wvu.FilterData" localSheetId="0" hidden="1">'Form Responses 1'!$A$1:$L$44</definedName>
   </definedNames>
   <calcPr calcId="0"/>
   <customWorkbookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="110">
   <si>
     <t>First Name</t>
   </si>
@@ -349,13 +349,25 @@
   </si>
   <si>
     <t>Editorial Review Board Members</t>
+  </si>
+  <si>
+    <t>Serdar</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Simsek</t>
+  </si>
+  <si>
+    <t>serdar.simsek@utdallas.edu</t>
+  </si>
+  <si>
+    <t>The University of Texas at Dallas</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -409,6 +421,13 @@
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="10"/>
+      <color theme="10"/>
+      <name val="Arial"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -474,10 +493,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -502,12 +522,14 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -725,7 +747,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Z998"/>
+  <dimension ref="A1:Z1000"/>
   <sheetFormatPr defaultColWidth="12.609375" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="18.88671875" style="2" customWidth="1"/>
@@ -792,7 +814,7 @@
       <c r="L2" s="4"/>
     </row>
     <row r="3" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A3" s="16" t="s">
+      <c r="A3" s="14" t="s">
         <v>104</v>
       </c>
       <c r="B3" s="3"/>
@@ -1049,222 +1071,259 @@
       <c r="Y9" s="7"/>
       <c r="Z9" s="7"/>
     </row>
-    <row r="10" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="17" t="s">
+    <row r="10" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A10" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="C10" s="18" t="s">
+        <v>108</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="G10" s="7"/>
+      <c r="H10" s="7"/>
+      <c r="I10" s="7"/>
+      <c r="J10" s="7"/>
+      <c r="K10" s="7"/>
+      <c r="L10" s="7"/>
+      <c r="M10" s="7"/>
+      <c r="N10" s="7"/>
+      <c r="O10" s="7"/>
+      <c r="P10" s="7"/>
+      <c r="Q10" s="7"/>
+      <c r="R10" s="7"/>
+      <c r="S10" s="7"/>
+      <c r="T10" s="7"/>
+      <c r="U10" s="7"/>
+      <c r="V10" s="7"/>
+      <c r="W10" s="7"/>
+      <c r="X10" s="7"/>
+      <c r="Y10" s="7"/>
+      <c r="Z10" s="7"/>
+    </row>
+    <row r="11" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A11" s="5"/>
+      <c r="B11" s="5"/>
+      <c r="C11" s="7"/>
+      <c r="D11" s="7"/>
+      <c r="E11" s="7"/>
+      <c r="F11" s="5"/>
+      <c r="G11" s="7"/>
+      <c r="H11" s="7"/>
+      <c r="I11" s="7"/>
+      <c r="J11" s="7"/>
+      <c r="K11" s="7"/>
+      <c r="L11" s="7"/>
+      <c r="M11" s="7"/>
+      <c r="N11" s="7"/>
+      <c r="O11" s="7"/>
+      <c r="P11" s="7"/>
+      <c r="Q11" s="7"/>
+      <c r="R11" s="7"/>
+      <c r="S11" s="7"/>
+      <c r="T11" s="7"/>
+      <c r="U11" s="7"/>
+      <c r="V11" s="7"/>
+      <c r="W11" s="7"/>
+      <c r="X11" s="7"/>
+      <c r="Y11" s="7"/>
+      <c r="Z11" s="7"/>
+    </row>
+    <row r="12" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A12" s="15" t="s">
         <v>105</v>
-      </c>
-    </row>
-    <row r="11" spans="1:26" ht="14.4" x14ac:dyDescent="0.55000000000000004">
-      <c r="A11" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="B11" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="C11" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="D11" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="E11" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="F11" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="G11" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="H11" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="I11" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="J11" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="K11" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="L11" s="9" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="12" spans="1:26" ht="14.4" x14ac:dyDescent="0.55000000000000004">
-      <c r="A12" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="B12" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="C12" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="D12" s="9" t="s">
-        <v>77</v>
-      </c>
-      <c r="E12" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="F12" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="G12" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="H12" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="I12" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="J12" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="K12" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="L12" s="9" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="13" spans="1:26" ht="14.4" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="9" t="s">
-        <v>82</v>
+        <v>65</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>83</v>
+        <v>66</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>84</v>
+        <v>67</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>85</v>
+        <v>68</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>86</v>
+        <v>69</v>
       </c>
       <c r="F13" s="10" t="s">
         <v>17</v>
       </c>
       <c r="G13" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="H13" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="H13" s="9" t="s">
-        <v>29</v>
-      </c>
       <c r="I13" s="9" t="s">
-        <v>87</v>
+        <v>21</v>
       </c>
       <c r="J13" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="K13" s="9"/>
-      <c r="L13" s="9"/>
+        <v>71</v>
+      </c>
+      <c r="K13" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="L13" s="9" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="14" spans="1:26" ht="14.4" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="9" t="s">
-        <v>89</v>
+        <v>74</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>92</v>
+        <v>77</v>
       </c>
       <c r="E14" s="9" t="s">
-        <v>93</v>
+        <v>78</v>
       </c>
       <c r="F14" s="10" t="s">
         <v>17</v>
       </c>
       <c r="G14" s="9" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="H14" s="9" t="s">
-        <v>29</v>
+        <v>70</v>
       </c>
       <c r="I14" s="9" t="s">
-        <v>94</v>
+        <v>30</v>
       </c>
       <c r="J14" s="9" t="s">
-        <v>32</v>
+        <v>79</v>
       </c>
       <c r="K14" s="9" t="s">
-        <v>95</v>
-      </c>
-      <c r="L14" s="9"/>
+        <v>80</v>
+      </c>
+      <c r="L14" s="9" t="s">
+        <v>81</v>
+      </c>
     </row>
     <row r="15" spans="1:26" ht="14.4" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="9" t="s">
-        <v>96</v>
+        <v>82</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>98</v>
+        <v>84</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>99</v>
+        <v>85</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>38</v>
+        <v>86</v>
       </c>
       <c r="F15" s="10" t="s">
         <v>17</v>
       </c>
       <c r="G15" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="H15" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="I15" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="J15" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="K15" s="9"/>
+      <c r="L15" s="9"/>
+    </row>
+    <row r="16" spans="1:26" ht="14.4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A16" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="B16" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="C16" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="D16" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="E16" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="F16" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="G16" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="H16" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="I16" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="J16" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="K16" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="L16" s="9"/>
+    </row>
+    <row r="17" spans="1:12" ht="14.4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A17" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="B17" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="C17" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="D17" s="9" t="s">
+        <v>99</v>
+      </c>
+      <c r="E17" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="F17" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="G17" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="H15" s="9" t="s">
+      <c r="H17" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="I15" s="9" t="s">
+      <c r="I17" s="9" t="s">
         <v>101</v>
       </c>
-      <c r="J15" s="9" t="s">
+      <c r="J17" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="K15" s="9" t="s">
+      <c r="K17" s="9" t="s">
         <v>102</v>
       </c>
-      <c r="L15" s="9" t="s">
+      <c r="L17" s="9" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="16" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A16" s="4"/>
-      <c r="B16" s="4"/>
-      <c r="C16" s="4"/>
-      <c r="D16" s="4"/>
-      <c r="E16" s="4"/>
-      <c r="F16" s="4"/>
-      <c r="G16" s="4"/>
-      <c r="H16" s="4"/>
-      <c r="I16" s="4"/>
-      <c r="J16" s="4"/>
-      <c r="K16" s="4"/>
-      <c r="L16" s="4"/>
-    </row>
-    <row r="17" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A17" s="4"/>
-      <c r="B17" s="4"/>
-      <c r="C17" s="4"/>
-      <c r="D17" s="4"/>
-      <c r="E17" s="4"/>
-      <c r="F17" s="4"/>
-      <c r="G17" s="4"/>
-      <c r="H17" s="4"/>
-      <c r="I17" s="4"/>
-      <c r="J17" s="4"/>
-      <c r="K17" s="4"/>
-      <c r="L17" s="4"/>
     </row>
     <row r="18" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="4"/>
@@ -1312,100 +1371,100 @@
       <c r="A21" s="4"/>
       <c r="B21" s="4"/>
       <c r="C21" s="4"/>
-      <c r="D21" s="3"/>
-      <c r="E21" s="3"/>
-      <c r="F21" s="7"/>
-      <c r="G21" s="3"/>
-      <c r="H21" s="3"/>
-      <c r="I21" s="3"/>
-      <c r="J21" s="3"/>
-      <c r="K21" s="3"/>
-      <c r="L21" s="3"/>
+      <c r="D21" s="4"/>
+      <c r="E21" s="4"/>
+      <c r="F21" s="4"/>
+      <c r="G21" s="4"/>
+      <c r="H21" s="4"/>
+      <c r="I21" s="4"/>
+      <c r="J21" s="4"/>
+      <c r="K21" s="4"/>
+      <c r="L21" s="4"/>
     </row>
     <row r="22" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="4"/>
       <c r="B22" s="4"/>
-      <c r="C22" s="3"/>
-      <c r="D22" s="3"/>
-      <c r="E22" s="3"/>
-      <c r="F22" s="3"/>
-      <c r="G22" s="3"/>
-      <c r="H22" s="3"/>
-      <c r="I22" s="3"/>
-      <c r="J22" s="3"/>
-      <c r="K22" s="3"/>
-      <c r="L22" s="3"/>
+      <c r="C22" s="4"/>
+      <c r="D22" s="4"/>
+      <c r="E22" s="4"/>
+      <c r="F22" s="4"/>
+      <c r="G22" s="4"/>
+      <c r="H22" s="4"/>
+      <c r="I22" s="4"/>
+      <c r="J22" s="4"/>
+      <c r="K22" s="4"/>
+      <c r="L22" s="4"/>
     </row>
     <row r="23" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A23" s="7"/>
-      <c r="B23" s="7"/>
-      <c r="C23" s="7"/>
-      <c r="D23" s="7"/>
-      <c r="E23" s="7"/>
+      <c r="A23" s="4"/>
+      <c r="B23" s="4"/>
+      <c r="C23" s="4"/>
+      <c r="D23" s="3"/>
+      <c r="E23" s="3"/>
       <c r="F23" s="7"/>
-      <c r="G23" s="7"/>
-      <c r="H23" s="7"/>
-      <c r="I23" s="7"/>
-      <c r="J23" s="7"/>
-      <c r="K23" s="7"/>
-      <c r="L23" s="7"/>
+      <c r="G23" s="3"/>
+      <c r="H23" s="3"/>
+      <c r="I23" s="3"/>
+      <c r="J23" s="3"/>
+      <c r="K23" s="3"/>
+      <c r="L23" s="3"/>
     </row>
     <row r="24" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A24" s="7"/>
-      <c r="B24" s="7"/>
-      <c r="C24" s="7"/>
-      <c r="D24" s="7"/>
-      <c r="E24" s="7"/>
-      <c r="F24" s="7"/>
-      <c r="G24" s="7"/>
-      <c r="H24" s="7"/>
-      <c r="I24" s="7"/>
-      <c r="J24" s="7"/>
-      <c r="K24" s="7"/>
-      <c r="L24" s="7"/>
-    </row>
-    <row r="25" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+      <c r="A24" s="4"/>
+      <c r="B24" s="4"/>
+      <c r="C24" s="3"/>
+      <c r="D24" s="3"/>
+      <c r="E24" s="3"/>
+      <c r="F24" s="3"/>
+      <c r="G24" s="3"/>
+      <c r="H24" s="3"/>
+      <c r="I24" s="3"/>
+      <c r="J24" s="3"/>
+      <c r="K24" s="3"/>
+      <c r="L24" s="3"/>
+    </row>
+    <row r="25" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A25" s="7"/>
+      <c r="B25" s="7"/>
+      <c r="C25" s="7"/>
+      <c r="D25" s="7"/>
+      <c r="E25" s="7"/>
+      <c r="F25" s="7"/>
+      <c r="G25" s="7"/>
+      <c r="H25" s="7"/>
+      <c r="I25" s="7"/>
+      <c r="J25" s="7"/>
+      <c r="K25" s="7"/>
+      <c r="L25" s="7"/>
+    </row>
     <row r="26" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A26" s="4"/>
-      <c r="B26" s="4"/>
-      <c r="C26" s="4"/>
-      <c r="D26" s="4"/>
-      <c r="E26" s="4"/>
-      <c r="F26" s="4"/>
-      <c r="G26" s="4"/>
-      <c r="H26" s="4"/>
-      <c r="I26" s="4"/>
-      <c r="J26" s="4"/>
-      <c r="K26" s="4"/>
-      <c r="L26" s="4"/>
-    </row>
-    <row r="27" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A27" s="11"/>
-      <c r="B27" s="11"/>
-      <c r="C27" s="11"/>
-      <c r="D27" s="11"/>
-      <c r="E27" s="11"/>
-      <c r="F27" s="11"/>
-      <c r="G27" s="11"/>
-      <c r="H27" s="11"/>
-      <c r="I27" s="11"/>
-      <c r="J27" s="11"/>
-      <c r="K27" s="11"/>
-      <c r="L27" s="11"/>
-    </row>
+      <c r="A26" s="7"/>
+      <c r="B26" s="7"/>
+      <c r="C26" s="7"/>
+      <c r="D26" s="7"/>
+      <c r="E26" s="7"/>
+      <c r="F26" s="7"/>
+      <c r="G26" s="7"/>
+      <c r="H26" s="7"/>
+      <c r="I26" s="7"/>
+      <c r="J26" s="7"/>
+      <c r="K26" s="7"/>
+      <c r="L26" s="7"/>
+    </row>
+    <row r="27" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
     <row r="28" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A28" s="12"/>
-      <c r="B28" s="12"/>
-      <c r="C28" s="12"/>
-      <c r="D28" s="13"/>
-      <c r="E28" s="13"/>
-      <c r="F28" s="13"/>
-      <c r="G28" s="13"/>
-      <c r="H28" s="13"/>
-      <c r="I28" s="7"/>
-      <c r="J28" s="7"/>
-      <c r="K28" s="11"/>
-      <c r="L28" s="11"/>
+      <c r="A28" s="4"/>
+      <c r="B28" s="4"/>
+      <c r="C28" s="4"/>
+      <c r="D28" s="4"/>
+      <c r="E28" s="4"/>
+      <c r="F28" s="4"/>
+      <c r="G28" s="4"/>
+      <c r="H28" s="4"/>
+      <c r="I28" s="4"/>
+      <c r="J28" s="4"/>
+      <c r="K28" s="4"/>
+      <c r="L28" s="4"/>
     </row>
     <row r="29" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" s="11"/>
@@ -1421,15 +1480,41 @@
       <c r="K29" s="11"/>
       <c r="L29" s="11"/>
     </row>
-    <row r="30" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="31" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="32" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="J32" s="14"/>
-      <c r="K32" s="15"/>
-      <c r="L32" s="15"/>
-    </row>
+    <row r="30" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A30" s="12"/>
+      <c r="B30" s="12"/>
+      <c r="C30" s="12"/>
+      <c r="D30" s="13"/>
+      <c r="E30" s="13"/>
+      <c r="F30" s="13"/>
+      <c r="G30" s="13"/>
+      <c r="H30" s="13"/>
+      <c r="I30" s="7"/>
+      <c r="J30" s="7"/>
+      <c r="K30" s="11"/>
+      <c r="L30" s="11"/>
+    </row>
+    <row r="31" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A31" s="11"/>
+      <c r="B31" s="11"/>
+      <c r="C31" s="11"/>
+      <c r="D31" s="11"/>
+      <c r="E31" s="11"/>
+      <c r="F31" s="11"/>
+      <c r="G31" s="11"/>
+      <c r="H31" s="11"/>
+      <c r="I31" s="11"/>
+      <c r="J31" s="11"/>
+      <c r="K31" s="11"/>
+      <c r="L31" s="11"/>
+    </row>
+    <row r="32" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
     <row r="33" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="34" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="34" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="J34" s="16"/>
+      <c r="K34" s="17"/>
+      <c r="L34" s="17"/>
+    </row>
     <row r="35" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
     <row r="36" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
     <row r="37" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
@@ -1437,22 +1522,22 @@
     <row r="39" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
     <row r="40" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
     <row r="41" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="42" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A42" s="3"/>
-      <c r="B42" s="3"/>
-      <c r="C42" s="3"/>
-      <c r="D42" s="3"/>
-      <c r="E42" s="3"/>
-      <c r="F42" s="3"/>
-      <c r="G42" s="3"/>
-      <c r="H42" s="3"/>
-      <c r="I42" s="3"/>
-      <c r="J42" s="3"/>
-      <c r="K42" s="14"/>
-      <c r="L42" s="15"/>
-    </row>
+    <row r="42" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
     <row r="43" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="44" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="44" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A44" s="3"/>
+      <c r="B44" s="3"/>
+      <c r="C44" s="3"/>
+      <c r="D44" s="3"/>
+      <c r="E44" s="3"/>
+      <c r="F44" s="3"/>
+      <c r="G44" s="3"/>
+      <c r="H44" s="3"/>
+      <c r="I44" s="3"/>
+      <c r="J44" s="3"/>
+      <c r="K44" s="16"/>
+      <c r="L44" s="17"/>
+    </row>
     <row r="45" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
     <row r="46" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
     <row r="47" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
@@ -2407,11 +2492,13 @@
     <row r="996" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
     <row r="997" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
     <row r="998" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="999" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
   </sheetData>
   <customSheetViews>
     <customSheetView guid="{B1502E2D-7D13-4985-8030-5AE29C7B5A5F}" filter="1" showAutoFilter="1">
       <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-      <autoFilter ref="A1:L43" xr:uid="{C5ADA987-59EE-4AF9-B34D-748BB015CB43}"/>
+      <autoFilter ref="A1:L43" xr:uid="{02070FD9-365E-4B29-8113-E2B0FCB85DFE}"/>
       <extLst>
         <ext uri="GoogleSheetsCustomDataVersion1">
           <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" filterViewId="641411698"/>
@@ -2420,13 +2507,14 @@
     </customSheetView>
   </customSheetViews>
   <mergeCells count="2">
-    <mergeCell ref="J32:L32"/>
-    <mergeCell ref="K42:L42"/>
+    <mergeCell ref="J34:L34"/>
+    <mergeCell ref="K44:L44"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="C4" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
     <hyperlink ref="C5" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
     <hyperlink ref="C6" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="C10" r:id="rId4" xr:uid="{D9AB0B29-6143-4631-BC7F-26711696B298}"/>
   </hyperlinks>
   <printOptions horizontalCentered="1" gridLines="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
